--- a/output/laminas_comunales/comunal_i_ingr_a_2021_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2021_aysen.xlsx
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,20 +588,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>886425.4399999999</v>
+          <t>Río Ibáñez</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -610,85 +602,61 @@
           <t>Chile Chico</t>
         </is>
       </c>
-      <c r="B3">
-        <v>867467.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cisnes</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>863178</v>
+          <t>Lago Verde</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cochrane</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>891282.38</v>
+          <t>Coyhaique</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>967406.25</v>
+          <t>Cisnes</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>883129.5600000001</v>
+          <t>Tortel</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>835407.6899999999</v>
+          <t>O'Higgins</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cochrane</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>772342.3100000001</v>
+          <t>Guaitecas</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tortel</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>942689.12</v>
+          <t>Aysén</t>
+        </is>
       </c>
     </row>
   </sheetData>
